--- a/nr-rm-adeli/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/nr-rm-adeli/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-06T10:53:29+00:00</t>
+    <t>2024-10-29T10:41:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -6157,7 +6157,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>89</v>
@@ -6273,7 +6273,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>89</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>89</v>
@@ -7187,7 +7187,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>89</v>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>89</v>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>89</v>
@@ -8217,7 +8217,7 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>89</v>
@@ -8333,7 +8333,7 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>89</v>
